--- a/配置文档/ActivityConfig.xlsx
+++ b/配置文档/ActivityConfig.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GameDev\Roblox_Y1\配置文档\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12420"/>
+    <workbookView windowWidth="27948" windowHeight="12420" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
+    <sheet name="DailyTaskConfig" sheetId="2" r:id="rId2"/>
+    <sheet name="LoginMilestoneData" sheetId="3" r:id="rId3"/>
+    <sheet name="OnlineRewardData" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
   <si>
     <t>子配置键</t>
   </si>
@@ -45,6 +53,231 @@
   </si>
   <si>
     <t>含义</t>
+  </si>
+  <si>
+    <t>DailyTaskConfig</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>struct</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>每日任务</t>
+  </si>
+  <si>
+    <t>LoginMilestoneData</t>
+  </si>
+  <si>
+    <t>累计登录奖励</t>
+  </si>
+  <si>
+    <t>OnlineRewardData</t>
+  </si>
+  <si>
+    <t>在线奖励</t>
+  </si>
+  <si>
+    <t>索引</t>
+  </si>
+  <si>
+    <t>任务类型</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>目标值</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Rewards</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>number_option</t>
+  </si>
+  <si>
+    <t>kv_string_array</t>
+  </si>
+  <si>
+    <t>GetItem</t>
+  </si>
+  <si>
+    <t>拾取道具</t>
+  </si>
+  <si>
+    <t>拾取50个道具</t>
+  </si>
+  <si>
+    <t>{Type=Gem, Count=3}</t>
+  </si>
+  <si>
+    <t>3钻石</t>
+  </si>
+  <si>
+    <t>拾取80个道具</t>
+  </si>
+  <si>
+    <t>{Type=Item,Id=105,Count=1}</t>
+  </si>
+  <si>
+    <t>GetNpc</t>
+  </si>
+  <si>
+    <t>拾取狗作者</t>
+  </si>
+  <si>
+    <t>拾取10个狗作者</t>
+  </si>
+  <si>
+    <t>OnlineTime</t>
+  </si>
+  <si>
+    <t>在线30分钟</t>
+  </si>
+  <si>
+    <t>{Type=Gem, Count=5}</t>
+  </si>
+  <si>
+    <t>4钻石</t>
+  </si>
+  <si>
+    <t>ForFriendPlay</t>
+  </si>
+  <si>
+    <t>和好友在同一房间</t>
+  </si>
+  <si>
+    <t>和2位好友在同一房间</t>
+  </si>
+  <si>
+    <t>{Type=Gem, Count=2}</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>需要消费的金额</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>LoginDays</t>
+  </si>
+  <si>
+    <t>Reward</t>
+  </si>
+  <si>
+    <t>kv_string</t>
+  </si>
+  <si>
+    <t>背包扩容卡X1</t>
+  </si>
+  <si>
+    <t>Type=Item,Id=104,Count=1</t>
+  </si>
+  <si>
+    <t>15钻石</t>
+  </si>
+  <si>
+    <t>Type=Gem, Count=15</t>
+  </si>
+  <si>
+    <t>双倍出售卡X3</t>
+  </si>
+  <si>
+    <t>Type=Item,Id=103,Count=3</t>
+  </si>
+  <si>
+    <t>30分钟力量卡X2</t>
+  </si>
+  <si>
+    <t>Type=Item,Id=106,Count=2</t>
+  </si>
+  <si>
+    <t>背包扩容卡X2</t>
+  </si>
+  <si>
+    <t>Type=Item,Id=104,Count=2</t>
+  </si>
+  <si>
+    <t>20钻石</t>
+  </si>
+  <si>
+    <t>Type=Gem, Count=20</t>
+  </si>
+  <si>
+    <t>时长</t>
+  </si>
+  <si>
+    <t>TargetMinutes</t>
+  </si>
+  <si>
+    <t>NPC卡X2</t>
+  </si>
+  <si>
+    <t>Type=Item,Id=107,Count=2</t>
+  </si>
+  <si>
+    <t>15分钟力量卡</t>
+  </si>
+  <si>
+    <t>Type=Item,Id=105,Count=1</t>
+  </si>
+  <si>
+    <t>双倍出售卡X1</t>
+  </si>
+  <si>
+    <t>Type=Item,Id=103,Count=1</t>
+  </si>
+  <si>
+    <t>2钻石</t>
+  </si>
+  <si>
+    <t>Type=Gem, Count=2</t>
+  </si>
+  <si>
+    <t>30分钟力量卡X1</t>
+  </si>
+  <si>
+    <t>Type=Item,Id=106,Count=1</t>
+  </si>
+  <si>
+    <t>Type=Gem, Count=3</t>
+  </si>
+  <si>
+    <t>背包扩容卡(一小时)</t>
+  </si>
+  <si>
+    <t>5钻石</t>
+  </si>
+  <si>
+    <t>Type=Gem, Count=5</t>
   </si>
 </sst>
 </file>
@@ -57,12 +290,39 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -74,14 +334,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -404,12 +656,42 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -530,141 +812,159 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -978,8 +1278,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
@@ -990,28 +1290,647 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E3" location="LoginMilestoneData!A1" display="LoginMilestoneData"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="2" width="16.9444444444444" customWidth="1"/>
+    <col min="3" max="3" width="35.8888888888889" customWidth="1"/>
+    <col min="4" max="5" width="17.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="32.1388888888889" customWidth="1"/>
+    <col min="7" max="7" width="16.3425925925926" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:7">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="1">
+        <v>50</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:7">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1">
+        <v>80</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" customFormat="1" spans="1:7">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:7">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:7">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="30.8518518518519" customWidth="1"/>
+    <col min="3" max="3" width="34.287037037037" customWidth="1"/>
+    <col min="4" max="4" width="28.7592592592593" customWidth="1"/>
+    <col min="5" max="5" width="23.3611111111111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="15.15" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="22.95" spans="1:5">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" customFormat="1" ht="22.95" spans="1:5">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:5">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" customFormat="1" ht="23" customHeight="1" spans="1:5">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" customFormat="1" ht="22.95" spans="1:5">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" customFormat="1" ht="15.15" spans="1:5">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="15.15" spans="1:5">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="9"/>
+    <col min="2" max="2" width="23.3240740740741" customWidth="1"/>
+    <col min="3" max="3" width="19.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="38.6203703703704" customWidth="1"/>
+    <col min="5" max="16384" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:4">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:4">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:4">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:4">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:4">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:4">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>45</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:4">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>55</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:4">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>65</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:4">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>75</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:4">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>90</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/配置文档/ActivityConfig.xlsx
+++ b/配置文档/ActivityConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12420" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="82">
   <si>
     <t>子配置键</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>{Type=Item,Id=105,Count=1}</t>
+  </si>
+  <si>
+    <t>15 分钟力量卡</t>
   </si>
   <si>
     <t>GetNpc</t>
@@ -1494,20 +1497,22 @@
       <c r="F5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
@@ -1524,22 +1529,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1">
         <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
@@ -1547,19 +1552,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>33</v>
@@ -1585,13 +1590,13 @@
   <sheetData>
     <row r="1" customFormat="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>20</v>
@@ -1602,13 +1607,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="15.15" spans="1:5">
@@ -1622,7 +1627,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="22.95" spans="1:5">
@@ -1633,10 +1638,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -1648,10 +1653,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -1663,10 +1668,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -1678,10 +1683,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" s="4"/>
     </row>
@@ -1693,10 +1698,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="5"/>
     </row>
@@ -1708,10 +1713,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="15.15" spans="1:5">
@@ -1722,10 +1727,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1752,7 +1757,7 @@
         <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>18</v>
@@ -1766,13 +1771,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
@@ -1786,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
@@ -1797,10 +1802,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
@@ -1811,10 +1816,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
@@ -1825,10 +1830,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
@@ -1839,10 +1844,10 @@
         <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -1853,10 +1858,10 @@
         <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:4">
@@ -1870,7 +1875,7 @@
         <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:4">
@@ -1881,10 +1886,10 @@
         <v>55</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -1895,10 +1900,10 @@
         <v>65</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:4">
@@ -1909,10 +1914,10 @@
         <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:4">
@@ -1923,10 +1928,10 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/配置文档/ActivityConfig.xlsx
+++ b/配置文档/ActivityConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GameDev\Roblox_Y1\配置文档\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lanran\Desktop\Gamedev\Roblox_Y1\配置文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
   <si>
     <t>子配置键</t>
   </si>
@@ -146,15 +146,6 @@
   </si>
   <si>
     <t>15 分钟力量卡</t>
-  </si>
-  <si>
-    <t>GetNpc</t>
-  </si>
-  <si>
-    <t>拾取狗作者</t>
-  </si>
-  <si>
-    <t>拾取10个狗作者</t>
   </si>
   <si>
     <t>OnlineTime</t>
@@ -1282,14 +1273,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="27.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="24.8888888888889" customWidth="1"/>
-    <col min="5" max="5" width="22.8888888888889" customWidth="1"/>
-    <col min="6" max="6" width="23.7777777777778" customWidth="1"/>
+    <col min="4" max="4" width="24.8916666666667" customWidth="1"/>
+    <col min="5" max="5" width="22.8916666666667" customWidth="1"/>
+    <col min="6" max="6" width="23.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1385,14 +1376,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="16.9444444444444" customWidth="1"/>
-    <col min="3" max="3" width="35.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="16.9416666666667" customWidth="1"/>
+    <col min="3" max="3" width="35.8916666666667" customWidth="1"/>
     <col min="4" max="5" width="17.8333333333333" customWidth="1"/>
-    <col min="6" max="6" width="32.1388888888889" customWidth="1"/>
-    <col min="7" max="7" width="16.3425925925926" customWidth="1"/>
+    <col min="6" max="6" width="32.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="16.3416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:7">
@@ -1512,16 +1503,16 @@
         <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="1">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
@@ -1529,44 +1520,21 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:7">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1580,23 +1548,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="30.8518518518519" customWidth="1"/>
-    <col min="3" max="3" width="34.287037037037" customWidth="1"/>
-    <col min="4" max="4" width="28.7592592592593" customWidth="1"/>
-    <col min="5" max="5" width="23.3611111111111" customWidth="1"/>
+    <col min="2" max="2" width="30.85" customWidth="1"/>
+    <col min="3" max="3" width="34.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="28.7583333333333" customWidth="1"/>
+    <col min="5" max="5" width="23.3583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>20</v>
@@ -1607,16 +1575,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" customFormat="1" ht="15.15" spans="1:5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="14.25" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -1627,10 +1595,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" ht="22.95" spans="1:5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="23.25" spans="1:5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1638,14 +1606,14 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" customFormat="1" ht="22.95" spans="1:5">
+    <row r="5" customFormat="1" ht="23.25" spans="1:5">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1653,14 +1621,14 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="15.15" spans="1:5">
+    <row r="6" customFormat="1" ht="14.25" spans="1:5">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1668,10 +1636,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -1683,14 +1651,14 @@
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" customFormat="1" ht="22.95" spans="1:5">
+    <row r="8" customFormat="1" ht="23.25" spans="1:5">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1698,14 +1666,14 @@
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" customFormat="1" ht="15.15" spans="1:5">
+    <row r="9" customFormat="1" ht="14.25" spans="1:5">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1713,13 +1681,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" ht="15.15" spans="1:5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="14.25" spans="1:5">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1727,10 +1695,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1743,12 +1711,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9"/>
-    <col min="2" max="2" width="23.3240740740741" customWidth="1"/>
+    <col min="2" max="2" width="23.325" customWidth="1"/>
     <col min="3" max="3" width="19.4166666666667" customWidth="1"/>
-    <col min="4" max="4" width="38.6203703703704" customWidth="1"/>
+    <col min="4" max="4" width="38.6166666666667" customWidth="1"/>
     <col min="5" max="16384" width="9"/>
   </cols>
   <sheetData>
@@ -1757,7 +1725,7 @@
         <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>18</v>
@@ -1771,13 +1739,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
@@ -1791,7 +1759,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
@@ -1802,10 +1770,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
@@ -1816,10 +1784,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
@@ -1830,10 +1798,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
@@ -1844,10 +1812,10 @@
         <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -1858,10 +1826,10 @@
         <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:4">
@@ -1875,7 +1843,7 @@
         <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:4">
@@ -1886,10 +1854,10 @@
         <v>55</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -1900,10 +1868,10 @@
         <v>65</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:4">
@@ -1914,10 +1882,10 @@
         <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:4">
@@ -1928,10 +1896,10 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/配置文档/ActivityConfig.xlsx
+++ b/配置文档/ActivityConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="26385" windowHeight="11775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="82">
   <si>
     <t>子配置键</t>
   </si>
@@ -127,10 +127,10 @@
     <t>GetItem</t>
   </si>
   <si>
-    <t>拾取道具</t>
-  </si>
-  <si>
-    <t>拾取50个道具</t>
+    <t>Pick up an item</t>
+  </si>
+  <si>
+    <t>Pick up 50 items</t>
   </si>
   <si>
     <t>{Type=Gem, Count=3}</t>
@@ -139,7 +139,7 @@
     <t>3钻石</t>
   </si>
   <si>
-    <t>拾取80个道具</t>
+    <t>Pick up 80 items</t>
   </si>
   <si>
     <t>{Type=Item,Id=105,Count=1}</t>
@@ -151,7 +151,7 @@
     <t>OnlineTime</t>
   </si>
   <si>
-    <t>在线30分钟</t>
+    <t>Stay online for 30 minutes</t>
   </si>
   <si>
     <t>{Type=Gem, Count=5}</t>
@@ -160,13 +160,22 @@
     <t>4钻石</t>
   </si>
   <si>
+    <t>GetDog</t>
+  </si>
+  <si>
+    <t>Pick up a dog</t>
+  </si>
+  <si>
+    <t>Pick up 10 dogs</t>
+  </si>
+  <si>
     <t>ForFriendPlay</t>
   </si>
   <si>
-    <t>和好友在同一房间</t>
-  </si>
-  <si>
-    <t>和2位好友在同一房间</t>
+    <t>Be in the same room as a friend</t>
+  </si>
+  <si>
+    <t>Be in the same room as 2 friends</t>
   </si>
   <si>
     <t>{Type=Gem, Count=2}</t>
@@ -936,7 +945,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -954,6 +963,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -1284,22 +1296,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1336,7 +1348,7 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
@@ -1376,8 +1388,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="16.9416666666667" customWidth="1"/>
     <col min="3" max="3" width="35.8916666666667" customWidth="1"/>
@@ -1453,10 +1465,10 @@
       <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="1">
@@ -1476,10 +1488,10 @@
       <c r="B5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="1">
@@ -1492,17 +1504,17 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:7">
+    <row r="6" customFormat="1" ht="27" spans="1:7">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="E6" s="1">
@@ -1522,19 +1534,42 @@
       <c r="B7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E7" s="1">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="27" spans="1:7">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1558,13 +1593,13 @@
   <sheetData>
     <row r="1" customFormat="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>20</v>
@@ -1575,13 +1610,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="14.25" spans="1:5">
@@ -1595,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="23.25" spans="1:5">
@@ -1606,10 +1641,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -1621,10 +1656,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -1636,10 +1671,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -1651,10 +1686,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E7" s="4"/>
     </row>
@@ -1666,10 +1701,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" s="5"/>
     </row>
@@ -1681,10 +1716,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="14.25" spans="1:5">
@@ -1695,10 +1730,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1725,7 +1760,7 @@
         <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>18</v>
@@ -1739,13 +1774,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
@@ -1759,7 +1794,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
@@ -1770,10 +1805,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
@@ -1784,10 +1819,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
@@ -1798,10 +1833,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
@@ -1812,10 +1847,10 @@
         <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -1826,10 +1861,10 @@
         <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:4">
@@ -1843,7 +1878,7 @@
         <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:4">
@@ -1854,10 +1889,10 @@
         <v>55</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -1868,10 +1903,10 @@
         <v>65</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:4">
@@ -1882,10 +1917,10 @@
         <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:4">
@@ -1896,10 +1931,10 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/配置文档/ActivityConfig.xlsx
+++ b/配置文档/ActivityConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="26385" windowHeight="11775" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>

--- a/配置文档/ActivityConfig.xlsx
+++ b/配置文档/ActivityConfig.xlsx
@@ -694,10 +694,10 @@
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <s:alignment vertical="center"/>
     </s:xf>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <s:alignment horizontal="center" vertical="center"/>
     </s:xf>
-    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <s:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <s:alignment horizontal="center" vertical="top" wrapText="1"/>
     </s:xf>
@@ -1101,12 +1101,12 @@
   <s:dimension ref="A1:F5"/>
   <s:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
   <s:cols>
-    <s:col width="16.6666666666667" customWidth="1" style="2" min="1" max="1"/>
-    <s:col width="29" customWidth="1" style="2" min="2" max="2"/>
-    <s:col width="27.3333333333333" customWidth="1" style="2" min="3" max="3"/>
-    <s:col width="24.8916666666667" customWidth="1" style="2" min="4" max="4"/>
-    <s:col width="22.8916666666667" customWidth="1" style="2" min="5" max="5"/>
-    <s:col width="23.775" customWidth="1" style="2" min="6" max="6"/>
+    <s:col width="16.6666666666667" customWidth="1" style="1" min="1" max="1"/>
+    <s:col width="29" customWidth="1" style="1" min="2" max="2"/>
+    <s:col width="27.3333333333333" customWidth="1" style="1" min="3" max="3"/>
+    <s:col width="24.8916666666667" customWidth="1" style="1" min="4" max="4"/>
+    <s:col width="22.8916666666667" customWidth="1" style="1" min="5" max="5"/>
+    <s:col width="23.775" customWidth="1" style="1" min="6" max="6"/>
   </s:cols>
   <s:sheetData>
     <s:row r="1">
@@ -1261,7 +1261,7 @@
       </s:c>
       <s:c r="F5" s="0" t="inlineStr">
         <s:is>
-          <s:t>ESC 挽留礼包：提示时长与在线奖励引用；与福利页共享每日领取记录，不额外发奖</s:t>
+          <s:t>ESC 一次性挽留礼包：仅本次进服后的指定分钟数之内提示，每个玩家永久只能领取一次</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -1283,114 +1283,114 @@
   <s:dimension ref="A1:G8"/>
   <s:sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <s:cols>
-    <s:col width="16.9416666666667" customWidth="1" style="2" min="2" max="2"/>
-    <s:col width="35.8916666666667" customWidth="1" style="2" min="3" max="3"/>
-    <s:col width="17.8333333333333" customWidth="1" style="2" min="4" max="5"/>
-    <s:col width="32.1416666666667" customWidth="1" style="2" min="6" max="6"/>
-    <s:col width="16.3416666666667" customWidth="1" style="2" min="7" max="7"/>
+    <s:col width="16.9416666666667" customWidth="1" style="1" min="2" max="2"/>
+    <s:col width="35.8916666666667" customWidth="1" style="1" min="3" max="3"/>
+    <s:col width="17.8333333333333" customWidth="1" style="1" min="4" max="5"/>
+    <s:col width="32.1416666666667" customWidth="1" style="1" min="6" max="6"/>
+    <s:col width="16.3416666666667" customWidth="1" style="1" min="7" max="7"/>
   </s:cols>
   <s:sheetData>
     <s:row r="1">
-      <s:c r="A1" s="1" t="inlineStr">
+      <s:c r="A1" s="2" t="inlineStr">
         <s:is>
           <s:t>索引</s:t>
         </s:is>
       </s:c>
-      <s:c r="B1" s="1" t="inlineStr">
+      <s:c r="B1" s="2" t="inlineStr">
         <s:is>
           <s:t>任务类型</s:t>
         </s:is>
       </s:c>
-      <s:c r="C1" s="1" t="inlineStr">
+      <s:c r="C1" s="2" t="inlineStr">
         <s:is>
           <s:t>名字</s:t>
         </s:is>
       </s:c>
-      <s:c r="D1" s="1" t="inlineStr">
+      <s:c r="D1" s="2" t="inlineStr">
         <s:is>
           <s:t>描述</s:t>
         </s:is>
       </s:c>
-      <s:c r="E1" s="1" t="inlineStr">
+      <s:c r="E1" s="2" t="inlineStr">
         <s:is>
           <s:t>目标值</s:t>
         </s:is>
       </s:c>
-      <s:c r="F1" s="1" t="inlineStr">
+      <s:c r="F1" s="2" t="inlineStr">
         <s:is>
           <s:t>奖励</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="2">
-      <s:c r="A2" s="1" t="inlineStr">
+      <s:c r="A2" s="2" t="inlineStr">
         <s:is>
           <s:t>Index</s:t>
         </s:is>
       </s:c>
-      <s:c r="B2" s="1" t="inlineStr">
+      <s:c r="B2" s="2" t="inlineStr">
         <s:is>
           <s:t>Type</s:t>
         </s:is>
       </s:c>
-      <s:c r="C2" s="1" t="inlineStr">
+      <s:c r="C2" s="2" t="inlineStr">
         <s:is>
           <s:t>Name</s:t>
         </s:is>
       </s:c>
-      <s:c r="D2" s="1" t="inlineStr">
+      <s:c r="D2" s="2" t="inlineStr">
         <s:is>
           <s:t>Desc</s:t>
         </s:is>
       </s:c>
-      <s:c r="E2" s="1" t="inlineStr">
+      <s:c r="E2" s="2" t="inlineStr">
         <s:is>
           <s:t>Target</s:t>
         </s:is>
       </s:c>
-      <s:c r="F2" s="1" t="inlineStr">
+      <s:c r="F2" s="2" t="inlineStr">
         <s:is>
           <s:t>Rewards</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="3">
-      <s:c r="A3" s="1" t="inlineStr">
+      <s:c r="A3" s="2" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B3" s="1" t="inlineStr">
+      <s:c r="B3" s="2" t="inlineStr">
         <s:is>
           <s:t>string</s:t>
         </s:is>
       </s:c>
-      <s:c r="C3" s="1" t="inlineStr">
+      <s:c r="C3" s="2" t="inlineStr">
         <s:is>
           <s:t>string</s:t>
         </s:is>
       </s:c>
-      <s:c r="D3" s="1" t="inlineStr">
+      <s:c r="D3" s="2" t="inlineStr">
         <s:is>
           <s:t>string</s:t>
         </s:is>
       </s:c>
-      <s:c r="E3" s="1" t="inlineStr">
+      <s:c r="E3" s="2" t="inlineStr">
         <s:is>
           <s:t>number_option</s:t>
         </s:is>
       </s:c>
-      <s:c r="F3" s="1" t="inlineStr">
+      <s:c r="F3" s="2" t="inlineStr">
         <s:is>
           <s:t>kv_string_array</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="4">
-      <s:c r="A4" s="1" t="n">
+      <s:c r="A4" s="2" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="B4" s="1" t="inlineStr">
+      <s:c r="B4" s="2" t="inlineStr">
         <s:is>
           <s:t>GetItem</s:t>
         </s:is>
@@ -1405,25 +1405,25 @@
           <s:t>Pick up 50 items</s:t>
         </s:is>
       </s:c>
-      <s:c r="E4" s="1" t="n">
+      <s:c r="E4" s="2" t="n">
         <s:v>50</s:v>
       </s:c>
-      <s:c r="F4" s="1" t="inlineStr">
+      <s:c r="F4" s="2" t="inlineStr">
         <s:is>
           <s:t>{Type=Gem, Count=3}</s:t>
         </s:is>
       </s:c>
-      <s:c r="G4" s="1" t="inlineStr">
+      <s:c r="G4" s="2" t="inlineStr">
         <s:is>
           <s:t>3钻石</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="5">
-      <s:c r="A5" s="1" t="n">
+      <s:c r="A5" s="2" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="B5" s="1" t="inlineStr">
+      <s:c r="B5" s="2" t="inlineStr">
         <s:is>
           <s:t>GetItem</s:t>
         </s:is>
@@ -1438,25 +1438,25 @@
           <s:t>Pick up 80 items</s:t>
         </s:is>
       </s:c>
-      <s:c r="E5" s="1" t="n">
+      <s:c r="E5" s="2" t="n">
         <s:v>80</s:v>
       </s:c>
-      <s:c r="F5" s="1" t="inlineStr">
+      <s:c r="F5" s="2" t="inlineStr">
         <s:is>
           <s:t>{Type=Item,Id=105,Count=1}</s:t>
         </s:is>
       </s:c>
-      <s:c r="G5" s="1" t="inlineStr">
+      <s:c r="G5" s="2" t="inlineStr">
         <s:is>
           <s:t>15 分钟力量卡</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="6" ht="27" customHeight="1" s="2">
-      <s:c r="A6" s="1" t="n">
+    <s:row r="6" ht="27" customHeight="1" s="1">
+      <s:c r="A6" s="2" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="B6" s="1" t="inlineStr">
+      <s:c r="B6" s="2" t="inlineStr">
         <s:is>
           <s:t>OnlineTime</s:t>
         </s:is>
@@ -1471,25 +1471,25 @@
           <s:t>Stay online for 30 minutes</s:t>
         </s:is>
       </s:c>
-      <s:c r="E6" s="1" t="n">
+      <s:c r="E6" s="2" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="F6" s="1" t="inlineStr">
+      <s:c r="F6" s="2" t="inlineStr">
         <s:is>
           <s:t>{Type=Gem, Count=5}</s:t>
         </s:is>
       </s:c>
-      <s:c r="G6" s="1" t="inlineStr">
+      <s:c r="G6" s="2" t="inlineStr">
         <s:is>
           <s:t>4钻石</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="7">
-      <s:c r="A7" s="1" t="n">
+      <s:c r="A7" s="2" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="B7" s="1" t="inlineStr">
+      <s:c r="B7" s="2" t="inlineStr">
         <s:is>
           <s:t>GetDog</s:t>
         </s:is>
@@ -1504,25 +1504,25 @@
           <s:t>Pick up 10 dogs</s:t>
         </s:is>
       </s:c>
-      <s:c r="E7" s="1" t="n">
+      <s:c r="E7" s="2" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="F7" s="1" t="inlineStr">
+      <s:c r="F7" s="2" t="inlineStr">
         <s:is>
           <s:t>{Type=Gem, Count=3}</s:t>
         </s:is>
       </s:c>
-      <s:c r="G7" s="1" t="inlineStr">
+      <s:c r="G7" s="2" t="inlineStr">
         <s:is>
           <s:t>3钻石</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="8" ht="27" customHeight="1" s="2">
-      <s:c r="A8" s="1" t="n">
+    <s:row r="8" ht="27" customHeight="1" s="1">
+      <s:c r="A8" s="2" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="B8" s="1" t="inlineStr">
+      <s:c r="B8" s="2" t="inlineStr">
         <s:is>
           <s:t>ForFriendPlay</s:t>
         </s:is>
@@ -1537,15 +1537,15 @@
           <s:t>Be in the same room as 2 friends</s:t>
         </s:is>
       </s:c>
-      <s:c r="E8" s="1" t="n">
+      <s:c r="E8" s="2" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="F8" s="1" t="inlineStr">
+      <s:c r="F8" s="2" t="inlineStr">
         <s:is>
           <s:t>{Type=Gem, Count=2}</s:t>
         </s:is>
       </s:c>
-      <s:c r="G8" s="1" t="inlineStr">
+      <s:c r="G8" s="2" t="inlineStr">
         <s:is>
           <s:t>3钻石</s:t>
         </s:is>
@@ -1565,80 +1565,80 @@
   <s:dimension ref="A1:E10"/>
   <s:sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <s:cols>
-    <s:col width="30.85" customWidth="1" style="2" min="2" max="2"/>
-    <s:col width="34.2833333333333" customWidth="1" style="2" min="3" max="3"/>
-    <s:col width="28.7583333333333" customWidth="1" style="2" min="4" max="4"/>
-    <s:col width="23.3583333333333" customWidth="1" style="2" min="5" max="5"/>
+    <s:col width="30.85" customWidth="1" style="1" min="2" max="2"/>
+    <s:col width="34.2833333333333" customWidth="1" style="1" min="3" max="3"/>
+    <s:col width="28.7583333333333" customWidth="1" style="1" min="4" max="4"/>
+    <s:col width="23.3583333333333" customWidth="1" style="1" min="5" max="5"/>
   </s:cols>
   <s:sheetData>
     <s:row r="1">
-      <s:c r="A1" s="1" t="inlineStr">
+      <s:c r="A1" s="2" t="inlineStr">
         <s:is>
           <s:t>等级</s:t>
         </s:is>
       </s:c>
-      <s:c r="B1" s="1" t="inlineStr">
+      <s:c r="B1" s="2" t="inlineStr">
         <s:is>
           <s:t>需要消费的金额</s:t>
         </s:is>
       </s:c>
-      <s:c r="C1" s="1" t="inlineStr">
+      <s:c r="C1" s="2" t="inlineStr">
         <s:is>
           <s:t>s</s:t>
         </s:is>
       </s:c>
-      <s:c r="D1" s="1" t="inlineStr">
+      <s:c r="D1" s="2" t="inlineStr">
         <s:is>
           <s:t>奖励</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="2">
-      <s:c r="A2" s="1" t="inlineStr">
+      <s:c r="A2" s="2" t="inlineStr">
         <s:is>
           <s:t>Index</s:t>
         </s:is>
       </s:c>
-      <s:c r="B2" s="1" t="inlineStr">
+      <s:c r="B2" s="2" t="inlineStr">
         <s:is>
           <s:t>LoginDays</s:t>
         </s:is>
       </s:c>
-      <s:c r="C2" s="1" t="inlineStr">
+      <s:c r="C2" s="2" t="inlineStr">
         <s:is>
           <s:t>Desc</s:t>
         </s:is>
       </s:c>
-      <s:c r="D2" s="1" t="inlineStr">
+      <s:c r="D2" s="2" t="inlineStr">
         <s:is>
           <s:t>Reward</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="3" ht="14.25" customHeight="1" s="2">
-      <s:c r="A3" s="1" t="inlineStr">
+    <s:row r="3" ht="14.25" customHeight="1" s="1">
+      <s:c r="A3" s="2" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B3" s="1" t="inlineStr">
+      <s:c r="B3" s="2" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
-      <s:c r="C3" s="1" t="inlineStr">
+      <s:c r="C3" s="2" t="inlineStr">
         <s:is>
           <s:t>string</s:t>
         </s:is>
       </s:c>
-      <s:c r="D3" s="1" t="inlineStr">
+      <s:c r="D3" s="2" t="inlineStr">
         <s:is>
           <s:t>kv_string</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="4" ht="23.25" customHeight="1" s="2">
-      <s:c r="A4" s="1" t="n">
+    <s:row r="4" ht="23.25" customHeight="1" s="1">
+      <s:c r="A4" s="2" t="n">
         <s:v>1</s:v>
       </s:c>
       <s:c r="B4" s="3" t="n">
@@ -1649,15 +1649,15 @@
           <s:t>背包扩容卡X1</s:t>
         </s:is>
       </s:c>
-      <s:c r="D4" s="1" t="inlineStr">
+      <s:c r="D4" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=104,Count=1</s:t>
         </s:is>
       </s:c>
       <s:c r="E4" s="5" t="n"/>
     </s:row>
-    <s:row r="5" ht="23.25" customHeight="1" s="2">
-      <s:c r="A5" s="1" t="n">
+    <s:row r="5" ht="23.25" customHeight="1" s="1">
+      <s:c r="A5" s="2" t="n">
         <s:v>2</s:v>
       </s:c>
       <s:c r="B5" s="3" t="n">
@@ -1668,15 +1668,15 @@
           <s:t>15钻石</s:t>
         </s:is>
       </s:c>
-      <s:c r="D5" s="1" t="inlineStr">
+      <s:c r="D5" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Gem, Count=15</s:t>
         </s:is>
       </s:c>
       <s:c r="E5" s="5" t="n"/>
     </s:row>
-    <s:row r="6" ht="14.25" customHeight="1" s="2">
-      <s:c r="A6" s="1" t="n">
+    <s:row r="6" ht="14.25" customHeight="1" s="1">
+      <s:c r="A6" s="2" t="n">
         <s:v>3</s:v>
       </s:c>
       <s:c r="B6" s="3" t="n">
@@ -1687,15 +1687,15 @@
           <s:t>双倍出售卡X3</s:t>
         </s:is>
       </s:c>
-      <s:c r="D6" s="1" t="inlineStr">
+      <s:c r="D6" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=103,Count=3</s:t>
         </s:is>
       </s:c>
-      <s:c r="E6" s="1" t="n"/>
-    </s:row>
-    <s:row r="7" ht="23" customHeight="1" s="2">
-      <s:c r="A7" s="1" t="n">
+      <s:c r="E6" s="2" t="n"/>
+    </s:row>
+    <s:row r="7" ht="23" customHeight="1" s="1">
+      <s:c r="A7" s="2" t="n">
         <s:v>4</s:v>
       </s:c>
       <s:c r="B7" s="3" t="n">
@@ -1706,15 +1706,15 @@
           <s:t>30分钟力量卡X2</s:t>
         </s:is>
       </s:c>
-      <s:c r="D7" s="1" t="inlineStr">
+      <s:c r="D7" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=106,Count=2</s:t>
         </s:is>
       </s:c>
       <s:c r="E7" s="5" t="n"/>
     </s:row>
-    <s:row r="8" ht="23.25" customHeight="1" s="2">
-      <s:c r="A8" s="1" t="n">
+    <s:row r="8" ht="23.25" customHeight="1" s="1">
+      <s:c r="A8" s="2" t="n">
         <s:v>5</s:v>
       </s:c>
       <s:c r="B8" s="3" t="n">
@@ -1725,15 +1725,15 @@
           <s:t>15钻石</s:t>
         </s:is>
       </s:c>
-      <s:c r="D8" s="1" t="inlineStr">
+      <s:c r="D8" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Gem, Count=15</s:t>
         </s:is>
       </s:c>
       <s:c r="E8" s="6" t="n"/>
     </s:row>
-    <s:row r="9" ht="14.25" customHeight="1" s="2">
-      <s:c r="A9" s="1" t="n">
+    <s:row r="9" ht="14.25" customHeight="1" s="1">
+      <s:c r="A9" s="2" t="n">
         <s:v>6</s:v>
       </s:c>
       <s:c r="B9" s="3" t="n">
@@ -1744,14 +1744,14 @@
           <s:t>背包扩容卡X2</s:t>
         </s:is>
       </s:c>
-      <s:c r="D9" s="1" t="inlineStr">
+      <s:c r="D9" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=104,Count=2</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="10" ht="14.25" customHeight="1" s="2">
-      <s:c r="A10" s="1" t="n">
+    <s:row r="10" ht="14.25" customHeight="1" s="1">
+      <s:c r="A10" s="2" t="n">
         <s:v>7</s:v>
       </s:c>
       <s:c r="B10" s="3" t="n">
@@ -1762,7 +1762,7 @@
           <s:t>20钻石</s:t>
         </s:is>
       </s:c>
-      <s:c r="D10" s="1" t="inlineStr">
+      <s:c r="D10" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Gem, Count=20</s:t>
         </s:is>
@@ -1782,254 +1782,254 @@
   <s:dimension ref="A1:D13"/>
   <s:sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <s:cols>
-    <s:col width="9" customWidth="1" style="2" min="1" max="1"/>
-    <s:col width="23.325" customWidth="1" style="2" min="2" max="2"/>
-    <s:col width="19.4166666666667" customWidth="1" style="2" min="3" max="3"/>
-    <s:col width="38.6166666666667" customWidth="1" style="2" min="4" max="4"/>
-    <s:col width="9" customWidth="1" style="2" min="5" max="16384"/>
+    <s:col width="9" customWidth="1" style="1" min="1" max="1"/>
+    <s:col width="23.325" customWidth="1" style="1" min="2" max="2"/>
+    <s:col width="19.4166666666667" customWidth="1" style="1" min="3" max="3"/>
+    <s:col width="38.6166666666667" customWidth="1" style="1" min="4" max="4"/>
+    <s:col width="9" customWidth="1" style="1" min="5" max="16384"/>
   </s:cols>
   <s:sheetData>
-    <s:row r="1" customFormat="1" s="1">
-      <s:c r="A1" s="1" t="inlineStr">
+    <s:row r="1" customFormat="1" s="2">
+      <s:c r="A1" s="2" t="inlineStr">
         <s:is>
           <s:t>索引</s:t>
         </s:is>
       </s:c>
-      <s:c r="B1" s="1" t="inlineStr">
+      <s:c r="B1" s="2" t="inlineStr">
         <s:is>
           <s:t>时长</s:t>
         </s:is>
       </s:c>
-      <s:c r="C1" s="1" t="inlineStr">
+      <s:c r="C1" s="2" t="inlineStr">
         <s:is>
           <s:t>描述</s:t>
         </s:is>
       </s:c>
-      <s:c r="D1" s="1" t="inlineStr">
+      <s:c r="D1" s="2" t="inlineStr">
         <s:is>
           <s:t>奖励</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="2" customFormat="1" s="1">
-      <s:c r="A2" s="1" t="inlineStr">
+    <s:row r="2" customFormat="1" s="2">
+      <s:c r="A2" s="2" t="inlineStr">
         <s:is>
           <s:t>Index</s:t>
         </s:is>
       </s:c>
-      <s:c r="B2" s="1" t="inlineStr">
+      <s:c r="B2" s="2" t="inlineStr">
         <s:is>
           <s:t>TargetMinutes</s:t>
         </s:is>
       </s:c>
-      <s:c r="C2" s="1" t="inlineStr">
+      <s:c r="C2" s="2" t="inlineStr">
         <s:is>
           <s:t>Desc</s:t>
         </s:is>
       </s:c>
-      <s:c r="D2" s="1" t="inlineStr">
+      <s:c r="D2" s="2" t="inlineStr">
         <s:is>
           <s:t>Reward</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="3" customFormat="1" s="1">
-      <s:c r="A3" s="1" t="inlineStr">
+    <s:row r="3" customFormat="1" s="2">
+      <s:c r="A3" s="2" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B3" s="1" t="inlineStr">
+      <s:c r="B3" s="2" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
-      <s:c r="C3" s="1" t="inlineStr">
+      <s:c r="C3" s="2" t="inlineStr">
         <s:is>
           <s:t>string</s:t>
         </s:is>
       </s:c>
-      <s:c r="D3" s="1" t="inlineStr">
+      <s:c r="D3" s="2" t="inlineStr">
         <s:is>
           <s:t>kv_string</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="4" customFormat="1" s="1">
-      <s:c r="A4" s="1" t="n">
+    <s:row r="4" customFormat="1" s="2">
+      <s:c r="A4" s="2" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="B4" s="1" t="n">
+      <s:c r="B4" s="2" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="C4" s="1" t="inlineStr">
+      <s:c r="C4" s="2" t="inlineStr">
         <s:is>
           <s:t>NPC卡X2</s:t>
         </s:is>
       </s:c>
-      <s:c r="D4" s="1" t="inlineStr">
+      <s:c r="D4" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=107,Count=2</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="5" customFormat="1" s="1">
-      <s:c r="A5" s="1" t="n">
+    <s:row r="5" customFormat="1" s="2">
+      <s:c r="A5" s="2" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="B5" s="1" t="n">
+      <s:c r="B5" s="2" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="C5" s="1" t="inlineStr">
+      <s:c r="C5" s="2" t="inlineStr">
         <s:is>
           <s:t>15分钟力量卡</s:t>
         </s:is>
       </s:c>
-      <s:c r="D5" s="1" t="inlineStr">
+      <s:c r="D5" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=105,Count=1</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="6" customFormat="1" s="1">
-      <s:c r="A6" s="1" t="n">
+    <s:row r="6" customFormat="1" s="2">
+      <s:c r="A6" s="2" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="B6" s="1" t="n">
+      <s:c r="B6" s="2" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="C6" s="1" t="inlineStr">
+      <s:c r="C6" s="2" t="inlineStr">
         <s:is>
           <s:t>双倍出售卡X1</s:t>
         </s:is>
       </s:c>
-      <s:c r="D6" s="1" t="inlineStr">
+      <s:c r="D6" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=103,Count=1</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="7" customFormat="1" s="1">
-      <s:c r="A7" s="1" t="n">
+    <s:row r="7" customFormat="1" s="2">
+      <s:c r="A7" s="2" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="B7" s="1" t="n">
+      <s:c r="B7" s="2" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="C7" s="1" t="inlineStr">
+      <s:c r="C7" s="2" t="inlineStr">
         <s:is>
           <s:t>2钻石</s:t>
         </s:is>
       </s:c>
-      <s:c r="D7" s="1" t="inlineStr">
+      <s:c r="D7" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Gem, Count=2</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="8" customFormat="1" s="1">
-      <s:c r="A8" s="1" t="n">
+    <s:row r="8" customFormat="1" s="2">
+      <s:c r="A8" s="2" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="B8" s="1" t="n">
+      <s:c r="B8" s="2" t="n">
         <s:v>35</s:v>
       </s:c>
-      <s:c r="C8" s="1" t="inlineStr">
+      <s:c r="C8" s="2" t="inlineStr">
         <s:is>
           <s:t>30分钟力量卡X1</s:t>
         </s:is>
       </s:c>
-      <s:c r="D8" s="1" t="inlineStr">
+      <s:c r="D8" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=106,Count=1</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="9">
-      <s:c r="A9" s="1" t="n">
+      <s:c r="A9" s="2" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="B9" s="1" t="n">
+      <s:c r="B9" s="2" t="n">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="C9" s="1" t="inlineStr">
+      <s:c r="C9" s="2" t="inlineStr">
         <s:is>
           <s:t>3钻石</s:t>
         </s:is>
       </s:c>
-      <s:c r="D9" s="1" t="inlineStr">
+      <s:c r="D9" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Gem, Count=3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="10">
-      <s:c r="A10" s="1" t="n">
+      <s:c r="A10" s="2" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="B10" s="1" t="n">
+      <s:c r="B10" s="2" t="n">
         <s:v>55</s:v>
       </s:c>
-      <s:c r="C10" s="1" t="inlineStr">
+      <s:c r="C10" s="2" t="inlineStr">
         <s:is>
           <s:t>背包扩容卡(一小时)</s:t>
         </s:is>
       </s:c>
-      <s:c r="D10" s="1" t="inlineStr">
+      <s:c r="D10" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=104,Count=1</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="11">
-      <s:c r="A11" s="1" t="n">
+      <s:c r="A11" s="2" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="B11" s="1" t="n">
+      <s:c r="B11" s="2" t="n">
         <s:v>65</s:v>
       </s:c>
-      <s:c r="C11" s="1" t="inlineStr">
+      <s:c r="C11" s="2" t="inlineStr">
         <s:is>
           <s:t>5钻石</s:t>
         </s:is>
       </s:c>
-      <s:c r="D11" s="1" t="inlineStr">
+      <s:c r="D11" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Gem, Count=5</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="12">
-      <s:c r="A12" s="1" t="n">
+      <s:c r="A12" s="2" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="B12" s="1" t="n">
+      <s:c r="B12" s="2" t="n">
         <s:v>75</s:v>
       </s:c>
-      <s:c r="C12" s="1" t="inlineStr">
+      <s:c r="C12" s="2" t="inlineStr">
         <s:is>
           <s:t>双倍出售卡X1</s:t>
         </s:is>
       </s:c>
-      <s:c r="D12" s="1" t="inlineStr">
+      <s:c r="D12" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=103,Count=1</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="13">
-      <s:c r="A13" s="1" t="n">
+      <s:c r="A13" s="2" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="B13" s="1" t="n">
+      <s:c r="B13" s="2" t="n">
         <s:v>90</s:v>
       </s:c>
-      <s:c r="C13" s="1" t="inlineStr">
+      <s:c r="C13" s="2" t="inlineStr">
         <s:is>
           <s:t>30分钟力量卡X1</s:t>
         </s:is>
       </s:c>
-      <s:c r="D13" s="1" t="inlineStr">
+      <s:c r="D13" s="2" t="inlineStr">
         <s:is>
           <s:t>Type=Item,Id=106,Count=1</s:t>
         </s:is>
@@ -2047,10 +2047,11 @@
     <s:pageSetUpPr/>
   </s:sheetPr>
   <s:dimension ref="A1:D3"/>
-  <s:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
+  <s:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
   <s:cols>
-    <s:col width="44.5" customWidth="1" style="2" min="1" max="1"/>
-    <s:col width="37" customWidth="1" style="2" min="2" max="2"/>
+    <s:col width="44.5" customWidth="1" style="1" min="1" max="1"/>
+    <s:col width="37" customWidth="1" style="1" min="2" max="2"/>
+    <s:col width="23" customWidth="1" style="1" min="3" max="3"/>
   </s:cols>
   <s:sheetData>
     <s:row r="1">
@@ -2091,27 +2092,29 @@
       </s:c>
       <s:c r="D2" s="0" t="inlineStr">
         <s:is>
-          <s:t>触发时长，单位：分钟。按当天累计在线时长计算，重进保留、UTC 零点重置。达到本值且引用奖励已解锁、未领取时，按 ESC 显示中央礼包，左侧提示可立即领取；关闭系统菜单后可点击领取。若引用奖励的 TargetMinutes 更大，须同时达到该门槛。</s:t>
+          <s:t>提示期限，单位：分钟。默认 5 表示本次进服后的前 5 分钟内按 ESC 即可显示，未满 5 分钟就能领取，不是在线满 5 分钟才解锁；达到 5 分钟后不再显示或领取。重登按新会话重新计时，但已经领取的玩家永久不再获得。符合条件时，显示礼包前先 Close 主界面 Main 以外的所有游戏弹窗，等关闭完成再显示礼包；系统 ESC 菜单保留。</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="3">
       <s:c r="A3" s="0" t="inlineStr">
         <s:is>
-          <s:t>string,number</s:t>
+          <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
       <s:c r="B3" s="0" t="inlineStr">
         <s:is>
-          <s:t>OnlineRewardId</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C3" s="0" t="n">
-        <s:v>1</s:v>
+          <s:t>Reward</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C3" s="0" t="inlineStr">
+        <s:is>
+          <s:t>Type=Item,Id=107,Count=2</s:t>
+        </s:is>
       </s:c>
       <s:c r="D3" s="0" t="inlineStr">
         <s:is>
-          <s:t>引用 OnlineRewardData 页签的 Index，必须填写存在的奖励编号。奖励解锁分钟数在该行 TargetMinutes 修改；奖励类型、道具 ID、数量在 Reward 修改：Type=Item,Id=107,Count=2 表示 107 号道具 2 个；Type=Gem,Count=5 表示 5 钻石。与福利页共享每天一次的领取资格，任一处领取后均不可重复领取；背包不足不消耗资格。</s:t>
+          <s:t>本一次性礼包的独立奖励。Type=Item,Id=107,Count=2 表示 107 号道具 2 个；Type=Gem,Count=5 表示 5 钻石。每个玩家永久只能领取一次，跨天、重登、重生都不重置；与每日在线奖励的领取记录互不影响，发奖失败不消耗资格，可在本次提示期限内重试。</s:t>
         </s:is>
       </s:c>
     </s:row>

--- a/配置文档/ActivityConfig.xlsx
+++ b/配置文档/ActivityConfig.xlsx
@@ -2109,7 +2109,7 @@
       </s:c>
       <s:c r="C3" s="0" t="inlineStr">
         <s:is>
-          <s:t>Type=Item,Id=107,Count=2</s:t>
+          <s:t>Type=Aura,Id=102,Count=1</s:t>
         </s:is>
       </s:c>
       <s:c r="D3" s="0" t="inlineStr">

--- a/配置文档/ActivityConfig.xlsx
+++ b/配置文档/ActivityConfig.xlsx
@@ -1491,17 +1491,17 @@
       </s:c>
       <s:c r="B7" s="2" t="inlineStr">
         <s:is>
-          <s:t>GetDog</s:t>
+          <s:t>GetNoob</s:t>
         </s:is>
       </s:c>
       <s:c r="C7" s="7" t="inlineStr">
         <s:is>
-          <s:t>Pick up a dog</s:t>
+          <s:t>Collect a noob</s:t>
         </s:is>
       </s:c>
       <s:c r="D7" s="7" t="inlineStr">
         <s:is>
-          <s:t>Pick up 10 dogs</s:t>
+          <s:t>Collect 10 noobs</s:t>
         </s:is>
       </s:c>
       <s:c r="E7" s="2" t="n">

--- a/配置文档/ActivityConfig.xlsx
+++ b/配置文档/ActivityConfig.xlsx
@@ -1415,7 +1415,7 @@
       </s:c>
       <s:c r="G4" s="2" t="inlineStr">
         <s:is>
-          <s:t>3钻石</s:t>
+          <s:t>3 Diamonds</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -1448,7 +1448,7 @@
       </s:c>
       <s:c r="G5" s="2" t="inlineStr">
         <s:is>
-          <s:t>15 分钟力量卡</s:t>
+          <s:t>Strength Card (15 Minutes) × 1</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -1481,7 +1481,7 @@
       </s:c>
       <s:c r="G6" s="2" t="inlineStr">
         <s:is>
-          <s:t>4钻石</s:t>
+          <s:t>5 Diamonds</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -1514,7 +1514,7 @@
       </s:c>
       <s:c r="G7" s="2" t="inlineStr">
         <s:is>
-          <s:t>3钻石</s:t>
+          <s:t>3 Diamonds</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -1547,7 +1547,7 @@
       </s:c>
       <s:c r="G8" s="2" t="inlineStr">
         <s:is>
-          <s:t>3钻石</s:t>
+          <s:t>2 Diamonds</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -1646,7 +1646,7 @@
       </s:c>
       <s:c r="C4" s="4" t="inlineStr">
         <s:is>
-          <s:t>背包扩容卡X1</s:t>
+          <s:t>Backpack Boost Card (1 Hour) × 1</s:t>
         </s:is>
       </s:c>
       <s:c r="D4" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </s:c>
       <s:c r="C5" s="4" t="inlineStr">
         <s:is>
-          <s:t>15钻石</s:t>
+          <s:t>15 Diamonds</s:t>
         </s:is>
       </s:c>
       <s:c r="D5" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </s:c>
       <s:c r="C6" s="4" t="inlineStr">
         <s:is>
-          <s:t>双倍出售卡X3</s:t>
+          <s:t>Double Sell Value Card × 3</s:t>
         </s:is>
       </s:c>
       <s:c r="D6" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </s:c>
       <s:c r="C7" s="4" t="inlineStr">
         <s:is>
-          <s:t>30分钟力量卡X2</s:t>
+          <s:t>Strength Card (30 Minutes) × 2</s:t>
         </s:is>
       </s:c>
       <s:c r="D7" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </s:c>
       <s:c r="C8" s="4" t="inlineStr">
         <s:is>
-          <s:t>15钻石</s:t>
+          <s:t>15 Diamonds</s:t>
         </s:is>
       </s:c>
       <s:c r="D8" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </s:c>
       <s:c r="C9" s="4" t="inlineStr">
         <s:is>
-          <s:t>背包扩容卡X2</s:t>
+          <s:t>Backpack Boost Card (1 Hour) × 2</s:t>
         </s:is>
       </s:c>
       <s:c r="D9" s="2" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </s:c>
       <s:c r="C10" s="4" t="inlineStr">
         <s:is>
-          <s:t>20钻石</s:t>
+          <s:t>20 Diamonds</s:t>
         </s:is>
       </s:c>
       <s:c r="D10" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </s:c>
       <s:c r="C4" s="2" t="inlineStr">
         <s:is>
-          <s:t>NPC卡X2</s:t>
+          <s:t>NoobCard × 2</s:t>
         </s:is>
       </s:c>
       <s:c r="D4" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </s:c>
       <s:c r="C5" s="2" t="inlineStr">
         <s:is>
-          <s:t>15分钟力量卡</s:t>
+          <s:t>Strength Card (15 Minutes) × 1</s:t>
         </s:is>
       </s:c>
       <s:c r="D5" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </s:c>
       <s:c r="C6" s="2" t="inlineStr">
         <s:is>
-          <s:t>双倍出售卡X1</s:t>
+          <s:t>Double Sell Value Card × 1</s:t>
         </s:is>
       </s:c>
       <s:c r="D6" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </s:c>
       <s:c r="C7" s="2" t="inlineStr">
         <s:is>
-          <s:t>2钻石</s:t>
+          <s:t>2 Diamonds</s:t>
         </s:is>
       </s:c>
       <s:c r="D7" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </s:c>
       <s:c r="C8" s="2" t="inlineStr">
         <s:is>
-          <s:t>30分钟力量卡X1</s:t>
+          <s:t>Strength Card (30 Minutes) × 1</s:t>
         </s:is>
       </s:c>
       <s:c r="D8" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </s:c>
       <s:c r="C9" s="2" t="inlineStr">
         <s:is>
-          <s:t>3钻石</s:t>
+          <s:t>3 Diamonds</s:t>
         </s:is>
       </s:c>
       <s:c r="D9" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </s:c>
       <s:c r="C10" s="2" t="inlineStr">
         <s:is>
-          <s:t>背包扩容卡(一小时)</s:t>
+          <s:t>Backpack Boost Card (1 Hour) × 1</s:t>
         </s:is>
       </s:c>
       <s:c r="D10" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </s:c>
       <s:c r="C11" s="2" t="inlineStr">
         <s:is>
-          <s:t>5钻石</s:t>
+          <s:t>5 Diamonds</s:t>
         </s:is>
       </s:c>
       <s:c r="D11" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </s:c>
       <s:c r="C12" s="2" t="inlineStr">
         <s:is>
-          <s:t>双倍出售卡X1</s:t>
+          <s:t>Double Sell Value Card × 1</s:t>
         </s:is>
       </s:c>
       <s:c r="D12" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </s:c>
       <s:c r="C13" s="2" t="inlineStr">
         <s:is>
-          <s:t>30分钟力量卡X1</s:t>
+          <s:t>Strength Card (30 Minutes) × 1</s:t>
         </s:is>
       </s:c>
       <s:c r="D13" s="2" t="inlineStr">
